--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_002/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cfd_002/extracted.xlsx
@@ -280,6 +280,11 @@
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1321,12 +1326,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>RANS CFD for pressure drop and flow split in crew module purge Y-junction at 20–60 CFM</t>
+          <t>RANS CFD prediction of pressure drop and flow split through crew module purge duct Y-junction at 20–60 CFM for fan sizing and control margin</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>FUN3D RANS CFD is used to predict total pressure drop and branch flow distribution through a crew module purge duct Y-junction across a flow range of 20–60 CFM. Results support fan sizing and control margin decisions ahead of CDR. Validation is available at 20 and 30 CFM against bench mockup data; the 45 and 60 CFM operating points are extrapolations without experimental anchor points.</t>
+          <t>FUN3D v13.5 RANS (SST k-ω) CFD model of an ECLSS crew module purge duct Y-junction used to predict total pressure drop and branch flow distribution across a 20–60 CFM operating envelope. Results support fan sizing and control margin decisions ahead of CDR. Validation data available at 20 and 30 CFM; 45 and 60 CFM are extrapolated. Porous jump model represents perforated screen. Upstream swirl, pulsation, and unsteady effects are not modeled.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1364,9 +1369,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1495,7 +1500,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>CFD must predict total pressure drop and branch flow split across the purge Y-junction at 20–60 CFM with sufficient fidelity to support fan sizing and control margin decisions before CDR.</t>
+          <t>CFD predictions of ΔP and branch flow split must be sufficiently accurate to support fan sizing and control margin decisions for the purge duct Y-junction across 20–60 CFM; combined ΔP uncertainty must be characterized and acceptable to the subsystem lead.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1522,7 +1527,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Incompressible steady RANS model (SST k-omega, second-order schemes) of the purge duct Y-junction on an unstructured tet-prism mesh up to 10.3M cells; porous jump model for the perforated screen.</t>
+          <t>Incompressible steady RANS (SST k-ω) simulation of the purge duct Y-junction using unstructured tet-prism meshes (up to 10.3M cells) with a porous jump boundary for the perforated screen; geometry from Purge Duct CAD Rev D.</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1539,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Bench Mockup Pressure and Flow Split Measurements</t>
+          <t>Lab Mockup Bench Test Data (20 and 30 CFM)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Laboratory measurements of total pressure drop at 20 CFM (70 Pa ±3 Pa) and 30 CFM (128 Pa ±5 Pa), and flow split at 30 CFM (60/40 ±2%), taken on a Y-junction mockup with pressure taps and a thermal mass flowmeter.</t>
+          <t>Pressure tap measurements (P1 upstream, P2 downstream of Y) and thermal mass flowmeter data from a laboratory mockup at 20 CFM (ΔP = 70 ± 3 Pa) and 30 CFM (ΔP = 128 ± 5 Pa), plus flow split at 30 CFM (60/40 ± 2%).</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1556,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Screen Porous Jump Vendor Coefficients</t>
+          <t>Vendor Porous Screen Loss Coefficients</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Vendor-supplied quadratic pressure-loss coefficients (K1=1.7e7 1/m², K2=3.2e3 1/m) for the perforated screen, derived from curve fit at Re=3–6×10³; used as model input with acknowledged extrapolation risk at 60 CFM.</t>
+          <t>Quadratic loss coefficients (K1 = 1.7e7 1/m², K2 = 3.2e3 1/m) derived from vendor curve fit at Re = 3–6×10³, used for the internal porous jump boundary representing the perforated screen.</t>
         </is>
       </c>
     </row>
@@ -1993,7 +1998,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study at 30 CFM</t>
+          <t>Pressure Drop Comparison at 20 CFM</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2008,12 +2013,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Three mesh levels (2.1M, 4.7M, 10.3M cells) were run at 30 CFM. Pressure drop changed +3.9% from coarse to medium and +1.8% from medium to fine; Richardson extrapolation indicates remaining discretization effect of approximately 2–3%.</t>
+          <t>CFD-predicted ΔP (fine grid, SST) compared against lab mockup pressure tap measurement at 20 CFM</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Richardson-extrapolated asymptotic solution</t>
+          <t>Lab mockup bench test, ΔP = 70 ± 3 Pa</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2023,12 +2028,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Richardson extrapolation</t>
+          <t>Test measurement uncertainty (±3 Pa) reported; combined CFD uncertainty not separately stated for this point</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Remaining discretization error ~2–3% on fine grid</t>
+          <t>CFD = 68 Pa; error = −2.9% relative to test</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2040,7 +2045,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Pressure Drop Comparison at 20 CFM</t>
+          <t>Pressure Drop Comparison at 30 CFM</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2050,12 +2055,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>CFD (fine grid, SST k-omega) predicted ΔP = 68 Pa versus bench measurement of 70 Pa ±3 Pa at 20 CFM.</t>
+          <t>CFD-predicted ΔP (fine grid, SST) compared against lab mockup pressure tap measurement at 30 CFM</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Bench mockup thermal mass flowmeter and pressure tap measurements</t>
+          <t>Lab mockup bench test, ΔP = 128 ± 5 Pa</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2065,12 +2070,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Experimental uncertainty (±3 Pa) and combined CFD uncertainty (±6.7% at 30 CFM)</t>
+          <t>Combined quadrature UQ: grid (~2.5%), inlet flowrate (±1%), porous media fit (±6%); overall ±6.7% on ΔP</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>-2.9% error relative to experiment</t>
+          <t>CFD = 124 Pa; error = −3.1% relative to test; combined CFD UQ = ±6.7%</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2082,7 +2087,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Pressure Drop Comparison at 30 CFM</t>
+          <t>Flow Split Comparison at 30 CFM</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2092,12 +2097,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>CFD (fine grid, SST k-omega) predicted ΔP = 124 Pa versus bench measurement of 128 Pa ±5 Pa at 30 CFM.</t>
+          <t>CFD-predicted branch flow split (62/38) compared against lab mockup thermal flowmeter measurement (60/40 ± 2%) at 30 CFM</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Bench mockup pressure tap measurements</t>
+          <t>Lab mockup bench test flow split = 60/40 ± 2%</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2107,12 +2112,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Quadrature of grid effects (~2.5%), inlet flowrate (±1%), porous media fit (±6%); total ±6.7%</t>
+          <t>Test uncertainty ±2 percentage points; CFD split uncertainty estimated ±2–3 percentage points dominated by turbulence model choice</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>-3.1% error relative to experiment</t>
+          <t>CFD 62/38 vs. test 60/40; deviation ~2 percentage points, within test uncertainty band</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2124,7 +2129,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Branch Flow Split Comparison at 30 CFM</t>
+          <t>Mesh Convergence Study (Richardson Extrapolation)</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2134,12 +2139,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>CFD predicted a 62/38 branch split versus measured 60/40 (±2%) at 30 CFM.</t>
+          <t>Three-level mesh refinement study (2.1M, 4.7M, 10.3M cells) for ΔP at 30 CFM to estimate discretization error</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Bench mockup thermal mass flowmeter on inlet leg</t>
+          <t>Extrapolated asymptotic value from Richardson extrapolation</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2149,12 +2154,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Experimental uncertainty ±2 percentage points; turbulence model sensitivity ±2–3 points</t>
+          <t>Richardson extrapolation / asymptotic convergence analysis</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>2 percentage point deviation on primary branch</t>
+          <t>ΔP change: +3.9% (coarse→medium), +1.8% (medium→fine); remaining discretization effect ~2–3% on fine grid</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2176,12 +2181,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>SA and SST k-omega turbulence models compared on the fine grid at 30 CFM. SA produced ΔP ~3% lower than SST; branch split within 1 percentage point. SST adopted for production based on superior separation capture at the inner lip, corroborated by smoke visualization.</t>
+          <t>Cross-check of SST k-ω versus Spalart-Allmaras (SA) turbulence model on fine grid for ΔP and flow split at 30 CFM; SST retained based on better separation capture corroborated by smoke visualization</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>SA (Spalart-Allmaras) baseline model</t>
+          <t>SA model results; smoke flow visualization at inner lip</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2191,12 +2196,12 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Model-form sensitivity perturbation</t>
+          <t>Model-form sensitivity: SA vs. SST difference used to bound turbulence model uncertainty contribution to split</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>~3% ΔP difference between SST and SA; &lt;1 percentage point split difference</t>
+          <t>SA ΔP ~3% lower than SST; branch split within 1 percentage point between models</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2350,12 +2355,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Evidence of version control, reproducible build, and archived run environment for the CFD solver</t>
+          <t>Simulation software is a recognized, version-controlled solver with traceable run provenance</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>FUN3D v13.5 (named, versioned release) used in double precision. Run logs archived with FUN3D hashes and compiler flags. Case directories, meshes, and input decks tracked in GitLab repo cfd-purge-duct at tag v0.7. A "how to rerun" note is posted to SharePoint. No explicit regression test suite or ISO quality certification cited, limiting this to level 3.</t>
+          <t>FUN3D v13.5 is identified by name and version. Runs executed on a named HPC cluster (Ames "Nereid"). Case directories, meshes, and input decks tracked in GitLab repo (tag v0.7) with FUN3D hashes and compiler flags archived. A "how to rerun" note is posted to SharePoint. No explicit reference to NASA software certification process or formal regression test suite, but version control and run traceability are documented.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2384,12 +2389,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Evidence that the solver correctly implements governing equations for incompressible RANS flow</t>
+          <t>Code has been verified against known solutions or benchmarks</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>FUN3D is a well-established NASA solver; second-order schemes for convection and gradients are stated. No explicit MMS study, benchmark problem comparison, or independent code-verification reference is cited in the report. Relying on solver reputation and version citation alone yields level 2.</t>
+          <t>FUN3D is a widely used NASA CFD code with an established development and verification history, implicitly supporting code correctness. The report does not cite specific MMS studies, analytical solution comparisons, or benchmark problem results performed as part of this activity. Code verification is inferred from FUN3D's pedigree rather than documented explicitly in this study.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2418,12 +2423,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with estimated remaining error below acceptable threshold for fan sizing</t>
+          <t>Mesh convergence study performed and remaining discretization error quantified</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three mesh levels (2.1M, 4.7M, 10.3M cells) evaluated at 30 CFM. Successive changes of +3.9% and +1.8% in ΔP with Richardson extrapolation estimating residual discretization effect of ~2–3%. Y+ targeting for near-wall resolution documented (y+ ≈ 1–2 on 30 CFM case). Study conducted at one flow rate only; no GCI formally computed.</t>
+          <t>Three mesh levels (2.1M, 4.7M, 10.3M cells) were run at 30 CFM. ΔP changed +3.9% and +1.8% across refinements. Richardson extrapolation suggests remaining discretization effect of ~2–3% on the fine grid. y+ ≈ 1–2 at the near-wall cells on the 30 CFM case. Contribution included in combined UQ (≈2.5%). Temporal discretization not assessed (steady solver).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2445,19 +2450,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>4</v>
-      </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Demonstrated convergence of iterative solver to tight residual targets with mass conservation verified</t>
+          <t>Iterative convergence demonstrated with appropriate residual targets and mass conservation checks</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>L2 residuals driven to &lt;1e-5 for continuity and momentum. Branch mass balance &lt;0.2%. Pressure-drop monitor shown flat over the last 1,000 iterations. Convergence criteria are quantitative, tightly specified, and monitored for all cases.</t>
+          <t>L2 residuals for continuity and momentum driven below 1×10⁻⁵. Branch mass balance verified to &lt;0.2%. Pressure-drop monitor confirmed flat over the last 1,000 iterations. These criteria are clearly stated and consistently applied across all flow-rate cases.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2482,16 +2487,16 @@
         <v>3</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Evidence of correct model setup including boundary conditions, geometry fidelity, and independent review</t>
+          <t>Model setup independently reviewed; boundary conditions and geometry verified against design intent</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions documented (prescribed volumetric inlet, ambient static outlet, no-slip adiabatic walls, internal porous jump surface). Geometry based on CAD Rev D with deliberate suppression of sub-mm features and retention of branch lip detail. Parameterized meshing journals and solver scripts support reproducibility. No independent third-party review of the setup is mentioned; assessment is by the same analyst.</t>
+          <t>Boundary conditions are described in detail (inlet volumetric flow, outlet static pressure, no-slip adiabatic walls, porous jump coefficients). Geometry derived from CAD Rev D with documented suppressions. GitLab tracking supports reproducibility. However, no explicit independent review or check by a second analyst is mentioned; mesh quality metrics (skewness, aspect ratio) are not reported beyond prism layer parameters. Results are posted to SharePoint with rerun instructions, which partially supports use-error control.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2520,12 +2525,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Justification of governing equation choices (incompressible RANS, turbulence model) with documented limitations</t>
+          <t>Governing equations and turbulence model selection are justified; known model limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Incompressible assumption justified by M &lt; 0.12. SST k-omega selected over SA based on better separation capture at the inner lip corroborated by smoke visualization. Wall treatment sensitivity quantified (scalable wall functions increase ΔP by ~6%). Limitations documented: no upstream swirl/pulsation, steady-only solutions, porous jump extrapolation risk at 60 CFM, no URANS/LES. Known gaps are explicit.</t>
+          <t>Incompressible assumption justified by M &lt; 0.12. SST k-ω selected over SA based on better capture of separation at the inner lip, corroborated by smoke visualization. Limitations explicitly documented: no upstream swirl/pulsation, steady-only (no URANS/LES), porous jump valid only to lower Re range. Wall function sensitivity (+6% in ΔP) tested and scalable wall functions rejected. Model form is well-reasoned with known gaps clearly stated.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2554,12 +2559,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, boundary conditions, and porous media coefficients characterized with uncertainty</t>
+          <t>Material properties, boundary conditions, and screen coefficients are traceable and their uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Fluid properties fixed at 295 K (constant, isothermal). Inlet flow rates prescribed at four values. Screen porous jump coefficients from vendor curve fit; ±15% perturbation used to quantify sensitivity (±6% on ΔP). Coefficients acknowledged to be extrapolated beyond their validated Re range at 60 CFM. Geometry from named CAD revision. Uncertainty in inlet flowrate setting (±1%) propagated. Some input data gaps (no updated screen coefficients at higher Re).</t>
+          <t>Fluid properties (ρ, μ, T) specified at constant 295 K. Inlet boundary conditions set by prescribed volumetric flow rates matching test conditions. Porous jump coefficients from vendor curve fit with Re range noted. Sensitivity to ±15% perturbation in K-values quantified (±6% in ΔP, &lt;1.5 points in split). Inlet flowrate uncertainty (±1%) propagated to ΔP (≈±1%). Input uncertainty included in combined UQ. Limitation noted that vendor data Re range does not cover 60 CFM.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2588,12 +2593,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Experimental test articles are representative of the flight configuration with documented sample characterization</t>
+          <t>Experimental test articles are described and representative of the simulation geometry</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single lab mockup is used for all test points. No information provided on number of specimens, dimensional characterization of the mockup versus flight hardware, screen sample characterization, or production representativeness. Only two flow conditions tested.</t>
+          <t>A laboratory mockup with pressure taps at P1 and P2 and a thermal mass flowmeter on the inlet leg is used. Only two test points are available (20 and 30 CFM). No description of number of repeat runs, specimen characterization, or how closely the mockup matches the flight geometry (beyond the implication of a bench-scale representation). Sample size and production-representativeness are not formally established.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2615,19 +2620,19 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation with stated measurement uncertainty, controlled test environment, and test standards referenced</t>
+          <t>Test conditions are controlled and instrumented with calibrated equipment and stated measurement uncertainties</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Pressure taps at stations P1 and P2 and a thermal mass flowmeter are described; measurement uncertainties stated (±3 Pa at 20 CFM, ±5 Pa at 30 CFM; ±2% on flow split). However, no instrument calibration records, environmental control data, or applicable test standards (ASTM, ISO) are cited. Only two facility points exist; 45 and 60 CFM have no experimental coverage.</t>
+          <t>Test measurement uncertainties are reported (±3 Pa at 20 CFM, ±5 Pa at 30 CFM; ±2% on flow split). Thermal mass flowmeter used for inlet flow. Pressure taps at defined stations. However, instrument calibration records, environmental controls, and applicable test standards (e.g., ASTM) are not referenced. Controlled isothermal conditions are implied but not formally documented.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2656,12 +2661,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD boundary conditions demonstrably match experimental test conditions with propagated uncertainty</t>
+          <t>CFD boundary conditions match experimental conditions; differences are quantified</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Inlet flow rates in CFD set to match experimental conditions (20 and 30 CFM). Fluid properties set at isothermal 295 K matching lab-like conditions. Inlet flowrate uncertainty (±1%) propagated through to ΔP contribution. Porous jump coefficients applied at same conditions as the bench test. No explicit documentation comparing CFD geometry to as-built mockup dimensions.</t>
+          <t>CFD inlet conditions (20, 30 CFM) directly match the two test points. Fluid properties set to match isothermal lab conditions (295 K, constant ρ and μ). Inlet flowrate uncertainty (±1%) explicitly propagated into CFD UQ budget. Outlet condition (101.3 kPa ambient static) consistent with open-exhaust bench setup. No mismatch between test and model boundary conditions is identified at the validated points.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2690,12 +2695,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of CFD predictions to experimental measurements with uncertainty bounds at multiple flow conditions</t>
+          <t>Quantitative comparison of CFD predictions to test data with uncertainty bands at multiple operating points</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Pressure drop compared at 20 CFM (CFD −2.9% vs. experiment) and 30 CFM (CFD −3.1% vs. experiment). Branch flow split compared at 30 CFM (62/38 CFD vs. 60/40 measured, within ±2 pp uncertainty). Combined CFD uncertainty of ±6.7% on ΔP at 30 CFM reported via quadrature. Comparisons are quantitative with stated experimental uncertainty. Only two validation points; no comparison at 45 or 60 CFM.</t>
+          <t>ΔP compared at two flow rates: −2.9% at 20 CFM, −3.1% at 30 CFM, both within test uncertainty bands. Flow split compared at 30 CFM: CFD 62/38 vs. test 60/40 ± 2%, within uncertainty. Combined UQ of ±6.7% on ΔP at 30 CFM computed by quadrature across grid, inlet, and porous media contributions. Branch split uncertainty ±2–3 percentage points. Comparison is quantitative and multi-metric, though limited to two flow-rate points.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2724,12 +2729,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly support fan sizing and control margin decisions and are measurable both computationally and experimentally</t>
+          <t>QoIs (ΔP and flow split) directly address the fan sizing and control margin decision</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Total pressure drop (ΔP) and branch flow split are the direct quantities required for fan sizing and control margin assessment. Both are computed by CFD and measured in the bench test using the same definitions (P1–P2 differential, flow fraction per branch). QoIs are clearly aligned with the engineering decision.</t>
+          <t>Total pressure drop (ΔP) and branch flow split are the primary outputs explicitly linked to the stated purpose of fan sizing and control margin. Both QoIs are measurable experimentally (pressure taps, flowmeter) and computed directly by the CFD model. The report demonstrates a clear chain from QoI to engineering decision. UQ is quantified for both QoIs, enabling margin assessment.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2758,12 +2763,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions span the intended operating range (20–60 CFM) with representative geometry and flow regime</t>
+          <t>Validation conditions span the intended operating envelope (20–60 CFM); geometry and physics regime match the COU</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation covers 20 and 30 CFM of a 20–60 CFM COU envelope; the 45 and 60 CFM points are explicitly unvalidated extrapolations. Upstream swirl and pulsation—acknowledged as possible in operation—are absent from both CFD and bench test. Porous jump coefficients extrapolated beyond their validated Re range at higher flows. The report itself flags these as limitations requiring additional data before CDR. Significant gap between validation conditions and full COU envelope reduces relevance.</t>
+          <t>Validation data cover only 20 and 30 CFM; 45 and 60 CFM are extrapolated without experimental anchor points. The report explicitly acknowledges this gap and recommends an additional facility point at 45–50 CFM. Upstream swirl and pulsation, which may occur in the actual COU, are not represented in the validation tests or the CFD. Porous jump coefficients are from vendor data at Re below the 60 CFM regime. The lab mockup geometry correspondence to flight hardware is not formally documented. These gaps limit confidence in the full COU envelope.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2948,7 +2953,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CFD model demonstrates adequate fidelity for the validated range (20–30 CFM): pressure drop predictions are within −3.1% of bench measurements (well within the ±6.7% combined uncertainty), flow split agrees within the experimental uncertainty band, and mesh convergence and solver convergence are well-documented. The model is accepted for use in fan sizing and control margin analysis with the following conditions: (1) an additional facility point at 45–50 CFM must be obtained to anchor extrapolation before CDR; (2) a resolved-screen or updated-coefficient case must be run to bound porous-jump bias at 60 CFM; (3) if upstream swirl &gt;0.2 turn-rate is anticipated, an inflow profile sensitivity study must be completed; and (4) the fine-grid setup must be frozen and archived as baseline v1.0 prior to CDR.</t>
+          <t>The CFD model is accepted for use in fan sizing and control margin decisions within the validated flow range of 20–30 CFM, where ΔP predictions agree with bench data to within ±3.1% and the combined uncertainty (±6.7%) is quantified and traceable. Flow split predictions at 30 CFM agree with test within measurement uncertainty. Mesh convergence, solver convergence, turbulence model sensitivity, and porous coefficient sensitivity are all documented. The model is accepted with the following conditions recorded: (1) predictions at 45 and 60 CFM are extrapolations carrying higher uncertainty — an additional facility point at 45–50 CFM is recommended before CDR to anchor that regime; (2) the porous jump model uses vendor coefficients outside their validated Re range at 60 CFM — a resolved-screen or updated-coefficient bracketing analysis should be completed; (3) if upstream swirl exceeding 0.2 turn-rate is anticipated, an inflow profile sensitivity study must bound the branch split impact; (4) the fine-grid setup should be frozen and archived as baseline v1.0 before further algorithm changes are made.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2958,7 +2963,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>L. Ng</t>
+          <t>L. Ng (author); A. Whitaker (subsystem lead, addressee)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
